--- a/important_mails_2026-06-07.xlsx
+++ b/important_mails_2026-06-07.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H242"/>
+  <dimension ref="A1:H231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -552,21 +552,127 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Sun, 7 Jun 2026 08:39:32 +0000</t>
+          <t>Sun, 7 Jun 2026 17:51:49 +0000</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Your Amazon.de Rechnungskorrektur Versand durch Amazon for 5/2026</t>
+          <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Dear Weihai US,
+We have recently restricted listings for the product(s) listed below on Amazon.com.
+Please initiate a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing. If this inventory is not removed within 30 days of this notification (by 07/06/2026), we may dispose of it in accordance with FBA policies.
+Thank you for your attention to this matter.
+Regards,
+Product Safety Team
+Amazon.com
+www.amazon.com
+Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
+Affected Product(s):
+B0DRTR7GYJ
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
+SPC-USAmazon-844427151517655</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 7 Jun 2026 19:32:37 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.ae Merchant Invoice for 5/2026</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.ae Merchant Invoice for 5/2026
+ 96
+Hello,
+We are writing to inform you that your electronic Merchant Invoice for the month of 5/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Tax Document Library . In your Tax Document Library, you will be able to view, download or print your invoice.
+The Amazon Services Team
+ عزيزي Shen zhen shi wei hai zhong xin ke ji you xian،
+نراسلك لإبلاغك بأن فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاص بك لشهر 5/2026 متاح الآن في حساب Seller Central الخاص بك.
+للوصول إلى فاتورة الخاص بك، انتقل إلى حساب Seller Central الخاص بك &gt; التقارير &gt; مكتبة المستندات الضريبية &gt; فواتير ضريبة رسم البائع.
+في حساب Seller Central الخاص بك، ستتمكن من عرض {documentType}$ الخاص بك أو تنزيله أو طباعته.
+إذا كانت لديك أي أسئلة، فالمرجو التواصل مع دعم البائع.
+ مع أطيب التحيات،
+Amazon.ae
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ We hope you found this message to be useful. However, if you'd rather not receive future e-mails of this sort from Amazon.com, please opt-out here.
+ Copyright 2026 Amazon, Inc, or its affilia</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 7 Jun 2026 08:39:32 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.de Rechnungskorrektur Versand durch Amazon for 5/2026</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.de Rechnungskorrektur Versand durch Amazon for 5/2026
  96
@@ -590,39 +696,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 07:48:24 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.es Factura Logística de Amazon for 5/2026
  96
@@ -649,39 +755,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 06:51:17 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 5/2026</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 5/2026
  96
@@ -708,39 +814,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 06:47:21 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Creditnota Verkoper for 5/2026</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Creditnota Verkoper for 5/2026
  96
@@ -760,39 +866,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 06:42:19 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 5/2026</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 5/2026
  96
@@ -819,39 +925,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 06:15:01 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnungskorrektur Verkäufer for 5/2026</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.de Rechnungskorrektur Verkäufer for 5/2026
  96
@@ -875,39 +981,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 06:12:39 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Korygująca Sprzedawcy for 5/2026</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Korygująca Sprzedawcy for 5/2026
  96
@@ -931,39 +1037,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 05:57:10 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 5/2026</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 5/2026
  96
@@ -981,39 +1087,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 05:54:32 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Verkoper for 5/2026</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Verkoper for 5/2026
  96
@@ -1037,39 +1143,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 05:42:06 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 5/2026
  96
@@ -1092,39 +1198,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 07:30:07 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>transparency-queue &lt;transparency-queue@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>成功进行 OPR 评估所需采取的措施</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>尊敬的Transparency(透明计划)客户：
 您好！感谢您在Transparency(透明计划)中注册您的商品。
@@ -1144,39 +1250,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 03:33:45 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1192,39 +1298,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 05:07:33 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (MtDohxu3JK)</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1244,39 +1350,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Tue, 2 Jun 2026 13:57:10 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (okvedC6bat)</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1296,39 +1402,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Tue, 2 Jun 2026 08:40:44 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1344,39 +1450,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 19:29:32 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (260520getf)</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1401,39 +1507,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 13:21:50 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1453,39 +1559,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 13:21:46 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1502,39 +1608,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 15:15:46 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1554,39 +1660,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 14:55:10 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1603,39 +1709,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 14:58:44 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1652,110 +1758,6 @@
 Thank you for selling in the Amazon Store,
 Amazon Services
 Help us improve your payment experience on Amaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 31 May 2026 14:55:36 +0000</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement Attempted
-Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
-On 05/31/26 14:55 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
- 234.38.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon store,
-Amazon Services
-Help us improve your payment experience on Ama</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 31 May 2026 14:55:10 +0000</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement Attempted
-Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
-On 05/31/26 14:54 BST, we initiated a transfer to your payment method (bank account ending in 191) in the amount of £
- 236.39.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To find out more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon store,
-Amazon Services
-Help us improve your payment experience on Ama</t>
         </is>
       </c>
     </row>
@@ -5404,7 +5406,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>货件/库存类</t>
+          <t>其他风险类</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5419,69 +5421,21 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Sun, 31 May 2026 20:10:01 +0000</t>
+          <t>Thu, 4 Jun 2026 12:46:25 +0000</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
+          <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Your Amazon-Fulfilled Inventory</t>
+          <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
-We recently notified you about the removal of your listing(s) for the product(s) listed below due to a safety recall.
-You were required to submit a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choice within 30 days of the notification sent on 30/04/2026. Since no removal order was submitted since the notification was sent, we have submitted a disposal order for this inventory in accordance with our FBA policies.
-For more information regarding the removal of your product(s), see the notification e-mail you received from our Seller Performance Team. If you have any further questions, please contact our Seller Support .
-Thank you for your attention to this matter.
-Yours faithfully,
-Fulfilment by Amazon Team
-Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
-Affected Product(s):
-B0FPC87B1W
- SPC-EUAmazon-1548114031558799</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 4 Jun 2026 12:46:25 +0000</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>提交商品合规文件，以避免商品被移除</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除
@@ -5535,39 +5489,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 00:17:48 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -5597,39 +5551,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:43:35 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $143.78 in an attempt to settle your Amazon seller account balance.
@@ -5645,39 +5599,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 01:13:32 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq5h330940)</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -5702,39 +5656,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 06:55:02 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (7kDrHSJf1h)</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -5754,39 +5708,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 03:26:42 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5802,39 +5756,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 13:57:34 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Iot4D83CtY)</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -5854,39 +5808,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 02:44:04 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (y8kVKdPDvp)</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -5906,39 +5860,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:33:15 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $105.47 in an attempt to settle your Amazon seller account balance.
@@ -5954,39 +5908,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 02:39:33 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (ZazNpo+O9J)</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -6012,39 +5966,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 02:56:06 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6060,39 +6014,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:45:41 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq4e6nl040)</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -6117,10 +6071,62 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 31 May 2026 14:55:36 +0000</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
+On 05/31/26 14:55 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
+ 234.38.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+Help us improve your payment experience on Ama</t>
+        </is>
+      </c>
+    </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -6135,44 +6141,44 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Fri, 8 May 2026 05:42:00 +0000</t>
+          <t>Sun, 31 May 2026 14:55:10 +0000</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Your FBA request is complete (zl4CmeMn1C)</t>
+          <t>Your payment is on the way</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral-europe.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-4422594-1144120
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
-------------------------------------------------------------------------------
-Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
-and EU wide.
-------------------------------------------------------------------------------
-Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-EUAmazon-1249046860357252</t>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
+On 05/31/26 14:54 BST, we initiated a transfer to your payment method (bank account ending in 191) in the amount of £
+ 236.39.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To find out more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+Help us improve your payment experience on Ama</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -6187,73 +6193,21 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Thu, 7 May 2026 18:10:42 +0000</t>
+          <t>Sat, 30 May 2026 14:37:25 +0000</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Your FBA request is complete (toabAY9R4I)</t>
+          <t>Tu pago está en camino</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral-europe.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-6481250-1667106
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
-------------------------------------------------------------------------------
-Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
-and EU wide.
-------------------------------------------------------------------------------
-Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-EUAmazon-1266639044756489</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 30 May 2026 14:37:25 +0000</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>Tu pago está en camino</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6270,39 +6224,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6322,39 +6276,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 14:43:44 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6374,39 +6328,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 14:42:27 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6426,39 +6380,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 14:51:20 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -6474,39 +6428,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Wed, 27 May 2026 13:35:40 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6523,39 +6477,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 14:39:47 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6575,39 +6529,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 15:30:35 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6627,39 +6581,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 15:29:45 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6676,39 +6630,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 14:22:00 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6728,39 +6682,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 13:54:11 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6780,39 +6734,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:21:19 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January - March 2026</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -6829,39 +6783,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:07:05 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January-March 2026</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -6878,39 +6832,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 14:48:57 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6930,39 +6884,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:42 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -6986,39 +6940,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:19 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -7042,39 +6996,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 13:46:45 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7094,39 +7048,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:49:45 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7146,39 +7100,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:47:51 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7198,39 +7152,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:36:52 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7250,39 +7204,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:51:22 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -7298,39 +7252,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:50:04 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7347,39 +7301,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:49:55 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7399,39 +7353,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:53:51 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -7448,40 +7402,40 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:31:42 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - PS -
  APPEAL</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - PS - APPEAL
@@ -7502,39 +7456,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:48 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7552,39 +7506,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:09:04 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7602,39 +7556,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:10:43 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7652,39 +7606,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:07:21 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7702,39 +7656,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 06:06:12 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>帮您免费一站式搞定VAT、EPR等合规问题！亚马逊合规服务商城现已正式上线！</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>亚马逊合规服务商城正式上线，一站式帮助卖家高效搞定欧洲站点的VAT、EPR等合规问题。
 			尊敬的 深圳市微海众信科技有限公司,
@@ -7764,39 +7718,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Wed, 27 May 2026 17:40:38 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -7815,40 +7769,40 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Wed, 27 May 2026 11:02:38 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ, MARKETPLACE: 1 - PS - APPEAL
@@ -7861,40 +7815,40 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:58:41 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.ca" &lt;cscompliance-docreview-vendor@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC - DOC REVIEW
@@ -7911,40 +7865,40 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:53:39 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -7961,40 +7915,40 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:49:38 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC - DOC REVIEW
@@ -8011,39 +7965,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:02:52 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -8063,40 +8017,40 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 02:57:24 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -8112,40 +8066,40 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 02:55:04 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.fr" &lt;cscompliance-docreview-seller@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A13V1IB3VIYZZH - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A13V1IB3VIYZZH - SPO - Seller Partner Outreach - Document Review
@@ -8161,39 +8115,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 17:11:27 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -8212,40 +8166,40 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:24:17 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -8261,40 +8215,40 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:03:38 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -8308,40 +8262,40 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:02:28 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -8355,40 +8309,40 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:07:57 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>Hello,
 We have reviewed your appeal request. We are rejecting your appeal because the detail page has an image of a child playing with the product. We request you take the following action:
@@ -8401,39 +8355,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 03:03:13 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -8453,39 +8407,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 07:42:16 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-de@amazon.com" &lt;fba-3p-buyability-improvement-de@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -8510,39 +8464,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 10:44:21 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-it@amazon.com" &lt;fba-3p-buyability-improvement-it@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -8567,40 +8521,40 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:51 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -8615,40 +8569,40 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:28 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -8662,40 +8616,40 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:15:37 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -8709,84 +8663,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 8 May 2026 11:37:14 +0000</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t>Votre facture pour les frais de paiement au titre de la REP pour
- les ventes sur Amazon.fr |   Your VAT invoice for EPR Pay on Behalf charges
- for Amazon.fr sales</t>
-        </is>
-      </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>Bonjour,
-Votre facture pour couvrant les frais de paiement au titre de la Responsabilité élargie du producteur (REP) pour les ventes sur Amazon.fr est désormais disponible.
-La facture comprend (1) les frais d’éco-contribution qu’Amazon a payé en votre nom pour les ventes de produits soumis à des obligations REP sur Amazon.fr au cours de la période de référence applicable et (2) les frais de service REP Nous payons en votre nom, pour les catégories de REP spécifiées dans le résumé au niveau de la catégorie et dans le résumé au niveau de l’ASIN.
-Pour accéder à votre facture REP Nous Payons en votre nom , ouvrez la pièce jointe de cet e-mail ou accédez à la section Factures des frais du vendeur et recherchez « REP Nous payons en votre nom » dans la colonne « Type de facture ».
-Pour afficher un résumé au niveau de la catégorie des frais facturés, des périodes de déclaration applicables et des catégories REP, accédez à la section Affichage des transactions avec les frais de service comme type de transaction, et recherchez « REP Nous payons en votre nom » dans la colonne « Détails sur le produit ».
-Pour afficher le détail au niveau de l’ASIN de vos frais d’éco-contribution REP, des pério</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:40 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -8802,39 +8711,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:32 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -8848,40 +8757,40 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:31 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -8897,39 +8806,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:08:15 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -8945,40 +8854,40 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 15:14:09 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -8994,39 +8903,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 15:14:03 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -9042,39 +8951,39 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:10:04 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -9090,39 +8999,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:10:01 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -9136,40 +9045,40 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:10:00 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -9185,39 +9094,39 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:07:29 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -9233,39 +9142,39 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 15:12:02 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -9281,40 +9190,40 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -9330,39 +9239,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 23:39:40 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para junio</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para junio
@@ -9391,39 +9300,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 17:10:26 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -9439,40 +9348,40 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 15:13:11 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Tu cuenta cumple ahora nuestros requisitos de registro a efectos
  fiscales en Europa</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -9497,39 +9406,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 15:09:37 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Twoje konto spełnia już europejskie wymagania Amazon dotyczące rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -9554,39 +9463,39 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 10:15:12 +0000</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -9616,39 +9525,39 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Tue, 26 May 2026 12:22:30 +0000 (UTC)</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>TikTok Shop &lt;tiktokshopseller@shop.tiktok.com&gt;</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>借助这些高潜力商品加速你的业务成长</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>96
  借助这些高潜力商品加速你的业务成长
@@ -9741,39 +9650,39 @@
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 17:10:44 +0000</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -9791,39 +9700,39 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 08:12:17 +0000</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>Il team di Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Nuova convalida dei numeri di spedizione attiva da oggi</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>96
  Aggiorniamo i parametri di convalida dei numeri di spedizione per le spedizioni con corrieri non affiliati, includendo controlli relativi alla lunghezza, al formato previsto del corriere e ai requisiti aggiuntivi relativi ai caratteri. Questo ci permetterà di elaborare il tuo inventario più velocemente.
@@ -9834,39 +9743,39 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 07:52:06 +0000</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>Disponible desde hoy la nueva validación del número de seguimiento</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>96
  Hemos añadido parámetros de validación del número de seguimiento en los envíos con transportistas no asociados para comprobar la longitud, formato previsto del transportista y requisitos de caracteres adicionales y así procesar tu inventario más rápido.
@@ -9878,39 +9787,39 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 17:10:56 +0000</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -9926,39 +9835,39 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 08:56:06 +0000</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>5月27日前入库助力Prime Day成功</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -9988,39 +9897,39 @@
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 14:06:09 +0000</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>Seller News: May 2026</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -10035,39 +9944,39 @@
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 13:00:10 +0000</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>Seller News: May 2026</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr"/>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -10082,39 +9991,39 @@
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 10:15:46 +0000</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr"/>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -10129,39 +10038,39 @@
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 15:00:47 +0000</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr"/>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -10176,39 +10085,39 @@
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 13:54:37 +0000</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -10223,39 +10132,39 @@
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 17:10:53 +0000</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr"/>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -10273,39 +10182,39 @@
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D189" s="2" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:55:42 +0000</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>Ship Smarter: Get 3 FREE Brokerage Fees: Limited Time C2S2 Offer 🚀</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr"/>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z3hy11/6664114770/h/cIM7P1R6ABFsNRmzeIU2ASpTCxzOevVrUjDi2lts12A)
 Ship Cross-Border &amp; Save Big. Get Started with C2S2 Today.
@@ -10322,39 +10231,39 @@
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 06:33:16 +0000</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr"/>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -10373,39 +10282,39 @@
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:48:46 +0000</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr"/>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -10420,40 +10329,40 @@
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 05:21:00 +0000</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr"/>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -10469,39 +10378,39 @@
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 17:10:29 +0000</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr"/>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -10517,39 +10426,39 @@
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:52:25 +0000</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;store-news@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>EchoPlan Magnetic Blocks is still in your cart</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr"/>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>Still thinking about it? https://www.amazon.com/gp/cart/view.html?ref_=cor
 EchoPlan 200PCS Magnetic Blocks, Magnetic Building Blocks, Magnet Blocks Cubes, STEM Educational Stacking Magnet Toy for Kids Ages 3 4 5 6 7 8 9 10 11, Birthday Gifts for Boys and Girls, 1&amp;quot; Large Size
@@ -10570,39 +10479,39 @@
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:07:42 +0000</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr"/>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -10617,39 +10526,39 @@
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 03:00:00 +0000</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr"/>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -10679,39 +10588,39 @@
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 16:40:18 +0000</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr"/>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -10739,39 +10648,39 @@
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:51:48 +0000</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>Pobierz raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr"/>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Możesz teraz pobrać kwartalny raport podatkowy, który zawiera dane, takie jak informacje identyfikacyjne, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -10787,39 +10696,39 @@
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 10:10:51 +0000</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>EPR Pay on Behalf charges for 2024 Amazon.co.uk sales</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr"/>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -10838,39 +10747,39 @@
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 12:21:34 +0000</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr"/>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -10892,39 +10801,39 @@
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:22:50 +0000</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr"/>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -10946,39 +10855,39 @@
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 16:23:48 +0000</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 4/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr"/>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -10997,39 +10906,39 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 08:34:05 +0000</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr"/>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -11041,39 +10950,39 @@
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:22:14 +0000</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr"/>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -11085,39 +10994,39 @@
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:02:56 +0000</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 4/2026</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr"/>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 4/2026 is now available in your Seller Central Account.
@@ -11129,39 +11038,39 @@
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:29:17 +0000</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr"/>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -11173,39 +11082,39 @@
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D207" s="2" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:25:39 +0000</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr"/>
-      <c r="H207" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -11217,39 +11126,39 @@
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:10:57 +0000</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr">
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr"/>
-      <c r="H208" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -11261,39 +11170,39 @@
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D209" s="2" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:09:44 +0000</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="F207" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr"/>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -11312,39 +11221,39 @@
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D210" s="2" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:01:18 +0000</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E208" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="F208" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr"/>
-      <c r="H210" s="2" t="inlineStr">
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -11363,39 +11272,39 @@
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:25:07 +0000</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F211" s="2" t="inlineStr">
+      <c r="F209" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 4 2026</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr"/>
-      <c r="H211" s="2" t="inlineStr">
+      <c r="G209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 4 i rok 2026.
@@ -11407,39 +11316,39 @@
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:24:35 +0000</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F212" s="2" t="inlineStr">
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr"/>
-      <c r="H212" s="2" t="inlineStr">
+      <c r="G210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -11451,39 +11360,39 @@
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D213" s="2" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:03:04 +0000</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F213" s="2" t="inlineStr">
+      <c r="F211" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr"/>
-      <c r="H213" s="2" t="inlineStr">
+      <c r="G211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -11495,39 +11404,39 @@
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D214" s="2" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 20:51:50 +0000</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F214" s="2" t="inlineStr">
+      <c r="F212" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr"/>
-      <c r="H214" s="2" t="inlineStr">
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -11539,39 +11448,39 @@
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D215" s="2" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:44:14 +0000</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F215" s="2" t="inlineStr">
+      <c r="F213" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 4 2026</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr"/>
-      <c r="H215" s="2" t="inlineStr">
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 4 i rok 2026.
@@ -11583,39 +11492,39 @@
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D216" s="2" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:35:59 +0000</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="E214" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F216" s="2" t="inlineStr">
+      <c r="F214" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr"/>
-      <c r="H216" s="2" t="inlineStr">
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -11627,39 +11536,39 @@
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B217" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C217" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D217" s="2" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:24:07 +0000</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="E215" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F217" s="2" t="inlineStr">
+      <c r="F215" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr"/>
-      <c r="H217" s="2" t="inlineStr">
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -11671,39 +11580,39 @@
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D218" s="2" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:18:06 +0000</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="E216" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F218" s="2" t="inlineStr">
+      <c r="F216" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr"/>
-      <c r="H218" s="2" t="inlineStr">
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -11715,39 +11624,39 @@
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D219" s="2" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:33:15 +0000</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F219" s="2" t="inlineStr">
+      <c r="F217" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G219" s="2" t="inlineStr"/>
-      <c r="H219" s="2" t="inlineStr">
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -11759,39 +11668,39 @@
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D220" s="2" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:20:52 +0000</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F220" s="2" t="inlineStr">
+      <c r="F218" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr"/>
-      <c r="H220" s="2" t="inlineStr">
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -11803,496 +11712,87 @@
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D221" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 8 May 2026 15:43:38 +0000</t>
-        </is>
-      </c>
-      <c r="E221" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F221" s="2" t="inlineStr">
-        <is>
-          <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
-        </is>
-      </c>
-      <c r="G221" s="2" t="inlineStr"/>
-      <c r="H221" s="2" t="inlineStr">
-        <is>
-          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
-We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
-Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
-In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
-Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
-Met vriendelijke groeten,
-Amazon.nl</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D222" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 8 May 2026 15:17:48 +0000</t>
-        </is>
-      </c>
-      <c r="E222" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F222" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
-        </is>
-      </c>
-      <c r="G222" s="2" t="inlineStr"/>
-      <c r="H222" s="2" t="inlineStr">
-        <is>
-          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
-We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
-To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
-In your Seller Central account, you will be able to view, download or print your invoice.
-If you have any questions, please contact Seller Support.
-Best regards,
-Amazon.co.uk</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D223" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 8 May 2026 14:52:53 +0000</t>
-        </is>
-      </c>
-      <c r="E223" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F223" s="2" t="inlineStr">
-        <is>
-          <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
-        </is>
-      </c>
-      <c r="G223" s="2" t="inlineStr"/>
-      <c r="H223" s="2" t="inlineStr">
-        <is>
-          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
-Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
-Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
-In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
-Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
-Freundliche Grüße,
-Amazon.de</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D224" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 8 May 2026 14:40:42 +0000</t>
-        </is>
-      </c>
-      <c r="E224" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F224" s="2" t="inlineStr">
-        <is>
-          <t>Je Factuur Verkoper Amazon.com.be voor 4/2026 (Votre Facture
- Vendeur Amazon.com.be pour le mois de 4/2026)</t>
-        </is>
-      </c>
-      <c r="G224" s="2" t="inlineStr"/>
-      <c r="H224" s="2" t="inlineStr">
-        <is>
-          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
-We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
-Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
-In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
-Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
-Met vriendelijke groeten,
-Amazon.com.be
- Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
-Nous vous écrivons pour vous informer que votre Facture Vendeur pour le mois de 4/2026 est maintenant disponible dans votre compte Seller Central.
-Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
-Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
-Pour toute question, contactez le Support Vendeur.
-Cordialement,
-Amazon.com.be</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D225" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 8 May 2026 13:57:28 +0000</t>
-        </is>
-      </c>
-      <c r="E225" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F225" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.co.uk Merchant Invoice for 4/2026</t>
-        </is>
-      </c>
-      <c r="G225" s="2" t="inlineStr"/>
-      <c r="H225" s="2" t="inlineStr">
-        <is>
-          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
-We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
-To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
-In your Seller Central account, you will be able to view, download or print your invoice.
-If you have any questions, please contact Seller Support.
-Best regards,
-Amazon.co.uk</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D226" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 8 May 2026 13:43:13 +0000</t>
-        </is>
-      </c>
-      <c r="E226" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F226" s="2" t="inlineStr">
-        <is>
-          <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
-        </is>
-      </c>
-      <c r="G226" s="2" t="inlineStr"/>
-      <c r="H226" s="2" t="inlineStr">
-        <is>
-          <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
-Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
-För att komma åt ditt fakturagår du till ditt Seller Central-konto &gt; Rapporter &gt; Bibliotek för skattedokument &gt; Skattefakturor för säljaravgifter.
-På ditt Seller Central-konto kan du se, ladda ner eller skriva ut ditt faktura.
-Om du har några frågor, kontakta säljarsupport.
-Vänliga hälsningar,
-Amazon.se</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D227" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 8 May 2026 13:40:52 +0000</t>
-        </is>
-      </c>
-      <c r="E227" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F227" s="2" t="inlineStr">
-        <is>
-          <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
-        </is>
-      </c>
-      <c r="G227" s="2" t="inlineStr"/>
-      <c r="H227" s="2" t="inlineStr">
-        <is>
-          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
-Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
-Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
-In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
-Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
-Freundliche Grüße,
-Amazon.de</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D228" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 8 May 2026 11:55:06 +0000</t>
-        </is>
-      </c>
-      <c r="E228" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F228" s="2" t="inlineStr">
-        <is>
-          <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 4.2026</t>
-        </is>
-      </c>
-      <c r="G228" s="2" t="inlineStr"/>
-      <c r="H228" s="2" t="inlineStr">
-        <is>
-          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
-Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
-Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
-In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
-Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
-Freundliche Grüße,
-Amazon.de</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B229" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C229" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D229" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 8 May 2026 11:49:29 +0000</t>
-        </is>
-      </c>
-      <c r="E229" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F229" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 4/2026</t>
-        </is>
-      </c>
-      <c r="G229" s="2" t="inlineStr"/>
-      <c r="H229" s="2" t="inlineStr">
-        <is>
-          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
-We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 4/2026 is now available in your Seller Central Account.
-To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
-In your Seller Central account, you will be able to view, download or print your invoice.
-If you have any questions, please contact Seller Support.
-Best regards,
-Amazon.co.uk</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B230" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D230" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 8 May 2026 11:20:15 +0000</t>
-        </is>
-      </c>
-      <c r="E230" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
-        </is>
-      </c>
-      <c r="F230" s="2" t="inlineStr">
-        <is>
-          <t>Dein Einkaufswagen wartet</t>
-        </is>
-      </c>
-      <c r="G230" s="2" t="inlineStr"/>
-      <c r="H230" s="2" t="inlineStr">
-        <is>
-          <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
-Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
- 23,49 €
-https://www.amazon.de/gp/product/B0DRCB74YN/?ref_=
-Einkaufswagen anzeigen
-https://www.amazon.de/gp/cart/view.html?ref_=cor
-Schaue dir weitere Optionen an
-75x120 cm Feuerfeste Unterlage, Hitzeschutzmatte, Antihaft-Material Bodenschutzmatte, Grill Matten, Bodenmatte Feuerstellenmatte Outdoor BBQ Matte für Gasgrill Holzkohlegrill
- 16,80 €
-https://www.amazon.de/gp/product/B0DBLM41YS/?ref_=ci_mcx_mr_2p_0_lm
-100 * 150cm Feuerfeste Unterlage - Hitzebeständig bis 1800°F Hitzeschutzmatte - Grillteppich Bodenschutzmatte Grillmatten Bodenmatte Feuerstellenmatte Outdoor BBQ Matte für Gasgrill Holzkohlegrill
- -17 % 25,19 € UVP: 30,24 €
-https://www.amazon.de/gp/product/B0BRTPDYMV/?ref_=ci_mcx_mr_2p_1_lm
-Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
- -4 % 20,15 € UVP: 20,97 €
-https://www.amazon.de/gp/product/B0CSGBZG8W/?ref_=ci_mc</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="2" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B231" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D231" s="2" t="inlineStr">
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 31 May 2026 20:10:01 +0000</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon-Fulfilled Inventory</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+We recently notified you about the removal of your listing(s) for the product(s) listed below due to a safety recall.
+You were required to submit a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choice within 30 days of the notification sent on 30/04/2026. Since no removal order was submitted since the notification was sent, we have submitted a disposal order for this inventory in accordance with our FBA policies.
+For more information regarding the removal of your product(s), see the notification e-mail you received from our Seller Performance Team. If you have any further questions, please contact our Seller Support .
+Thank you for your attention to this matter.
+Yours faithfully,
+Fulfilment by Amazon Team
+Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
+Affected Product(s):
+B0FPC87B1W
+ SPC-EUAmazon-1548114031558799</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 04:57:03 +0000</t>
         </is>
       </c>
-      <c r="E231" s="2" t="inlineStr">
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F231" s="2" t="inlineStr">
+      <c r="F220" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-11</t>
         </is>
       </c>
-      <c r="G231" s="2" t="inlineStr"/>
-      <c r="H231" s="2" t="inlineStr">
+      <c r="G220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -12315,39 +11815,39 @@
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B232" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C232" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D232" s="2" t="inlineStr">
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 03:41:21 +0000</t>
         </is>
       </c>
-      <c r="E232" s="2" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F232" s="2" t="inlineStr">
+      <c r="F221" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G232" s="2" t="inlineStr"/>
-      <c r="H232" s="2" t="inlineStr">
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -12371,39 +11871,39 @@
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B233" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C233" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D233" s="2" t="inlineStr">
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 03:00:56 +0000</t>
         </is>
       </c>
-      <c r="E233" s="2" t="inlineStr">
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F233" s="2" t="inlineStr">
+      <c r="F222" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr"/>
-      <c r="H233" s="2" t="inlineStr">
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -12426,39 +11926,39 @@
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B234" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C234" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D234" s="2" t="inlineStr">
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
         <is>
           <t>Sat, 23 May 2026 04:06:08 +0000</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="E223" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F234" s="2" t="inlineStr">
+      <c r="F223" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-04</t>
         </is>
       </c>
-      <c r="G234" s="2" t="inlineStr"/>
-      <c r="H234" s="2" t="inlineStr">
+      <c r="G223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -12481,39 +11981,39 @@
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B235" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C235" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D235" s="2" t="inlineStr">
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
         <is>
           <t>Sat, 23 May 2026 03:17:21 +0000</t>
         </is>
       </c>
-      <c r="E235" s="2" t="inlineStr">
+      <c r="E224" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F235" s="2" t="inlineStr">
+      <c r="F224" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G235" s="2" t="inlineStr"/>
-      <c r="H235" s="2" t="inlineStr">
+      <c r="G224" s="2" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -12537,39 +12037,39 @@
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B236" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C236" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D236" s="2" t="inlineStr">
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 04:51:55 +0000</t>
         </is>
       </c>
-      <c r="E236" s="2" t="inlineStr">
+      <c r="E225" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F236" s="2" t="inlineStr">
+      <c r="F225" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G236" s="2" t="inlineStr"/>
-      <c r="H236" s="2" t="inlineStr">
+      <c r="G225" s="2" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -12593,39 +12093,39 @@
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B237" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D237" s="2" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:58:34 +0000</t>
         </is>
       </c>
-      <c r="E237" s="2" t="inlineStr">
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F237" s="2" t="inlineStr">
+      <c r="F226" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G237" s="2" t="inlineStr"/>
-      <c r="H237" s="2" t="inlineStr">
+      <c r="G226" s="2" t="inlineStr"/>
+      <c r="H226" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -12646,39 +12146,39 @@
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B238" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D238" s="2" t="inlineStr">
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:50:26 +0000</t>
         </is>
       </c>
-      <c r="E238" s="2" t="inlineStr">
+      <c r="E227" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F238" s="2" t="inlineStr">
+      <c r="F227" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G238" s="2" t="inlineStr"/>
-      <c r="H238" s="2" t="inlineStr">
+      <c r="G227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -12701,39 +12201,39 @@
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D239" s="2" t="inlineStr">
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 04:43:42 +0000</t>
         </is>
       </c>
-      <c r="E239" s="2" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F239" s="2" t="inlineStr">
+      <c r="F228" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-21</t>
         </is>
       </c>
-      <c r="G239" s="2" t="inlineStr"/>
-      <c r="H239" s="2" t="inlineStr">
+      <c r="G228" s="2" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -12757,39 +12257,39 @@
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 03:34:49 +0000</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="E229" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F240" s="2" t="inlineStr">
+      <c r="F229" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G240" s="2" t="inlineStr"/>
-      <c r="H240" s="2" t="inlineStr">
+      <c r="G229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -12812,40 +12312,40 @@
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D241" s="2" t="inlineStr">
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 07:25:40 +0000</t>
         </is>
       </c>
-      <c r="E241" s="2" t="inlineStr">
+      <c r="E230" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F241" s="2" t="inlineStr">
+      <c r="F230" s="2" t="inlineStr">
         <is>
           <t>Update VAT registration information to reinstate Inventory and FBA
  functionality of your Amazon.it store</t>
         </is>
       </c>
-      <c r="G241" s="2" t="inlineStr"/>
-      <c r="H241" s="2" t="inlineStr">
+      <c r="G230" s="2" t="inlineStr"/>
+      <c r="H230" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -12861,39 +12361,39 @@
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B242" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D242" s="2" t="inlineStr">
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 11:38:29 +0000</t>
         </is>
       </c>
-      <c r="E242" s="2" t="inlineStr">
+      <c r="E231" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F242" s="2" t="inlineStr">
+      <c r="F231" s="2" t="inlineStr">
         <is>
           <t>You have until July 11 to verify FBA dimensions for fee calculation</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr"/>
-      <c r="H242" s="2" t="inlineStr">
+      <c r="G231" s="2" t="inlineStr"/>
+      <c r="H231" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
  96
